--- a/data/sample_demand.xlsx
+++ b/data/sample_demand.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>233</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>240</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>119.4</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="39">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>123</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="40">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>128.4</v>
+        <v>136.2</v>
       </c>
     </row>
     <row r="41">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>138</v>
+        <v>146.4</v>
       </c>
     </row>
     <row r="43">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>133.8</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>123</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="45">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>122.4</v>
+        <v>121.2</v>
       </c>
     </row>
     <row r="46">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>118.2</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="47">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>118.2</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="48">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>124.2</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="49">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>126.6</v>
+        <v>121.2</v>
       </c>
     </row>
     <row r="50">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>135.6</v>
+        <v>131.4</v>
       </c>
     </row>
     <row r="51">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>146.4</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="53">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>150.6</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>139.8</v>
+        <v>154.2</v>
       </c>
     </row>
     <row r="55">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>142.2</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>136.2</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="57">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>130.2</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="58">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>129</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="59">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>136.8</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="60">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>127.8</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="61">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>142.2</v>
+        <v>136.2</v>
       </c>
     </row>
     <row r="62">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>136.8</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>150</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="64">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>157.8</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="65">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>162.6</v>
+        <v>159.6</v>
       </c>
     </row>
     <row r="66">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>162.6</v>
+        <v>158.4</v>
       </c>
     </row>
     <row r="67">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>159.6</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="68">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>149.4</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="69">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>146.4</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>141</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="72">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>138.6</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="73">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>144.6</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="74">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>240</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>60</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="85">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>245</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>337</v>
+        <v>251</v>
       </c>
     </row>
     <row r="88">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>75</v>
+        <v>227</v>
       </c>
     </row>
     <row r="91">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>73</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>67</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>65</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="99">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>163</v>
+        <v>293</v>
       </c>
     </row>
     <row r="101">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>226</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>69</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="108">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="109">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>74</v>
+        <v>157</v>
       </c>
     </row>
     <row r="110">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="146">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="170">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>663</v>
       </c>
     </row>
     <row r="188">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>291</v>
+        <v>27</v>
       </c>
     </row>
     <row r="197">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
     </row>
     <row r="200">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203">
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>265</v>
+        <v>38</v>
       </c>
     </row>
     <row r="209">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
     </row>
     <row r="212">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="215">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="223">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0</v>
+        <v>916</v>
       </c>
     </row>
     <row r="226">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="229">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="235">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
     </row>
     <row r="238">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="241">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>172</v>
+        <v>43</v>
       </c>
     </row>
     <row r="247">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>293</v>
+        <v>527</v>
       </c>
     </row>
     <row r="250">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="253">
